--- a/docs/calibration/figures/jh4_shmtrace/tables.xlsx
+++ b/docs/calibration/figures/jh4_shmtrace/tables.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Run" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Samples" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Variants" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Positional" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Spectrum" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spectrum" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,19 +595,20 @@
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
     <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
-    <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,65 +754,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>mutation_frequency_observed_x1e3</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>mutated_reads_pct</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pct_GC</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pct_transitions</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pct_CT_GA</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>s5f_index</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>s5f_p</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pct_AT_in_WA_TW</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>analysed_bp</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>null_from</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>model_used</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -838,19 +844,19 @@
         <v>221</v>
       </c>
       <c r="F2" t="n">
-        <v>83.755</v>
+        <v>83.748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.379</v>
+        <v>0.378952</v>
       </c>
       <c r="H2" t="n">
-        <v>83.755</v>
+        <v>83.748</v>
       </c>
       <c r="I2" t="n">
-        <v>83.755</v>
+        <v>83.748</v>
       </c>
       <c r="J2" t="n">
-        <v>85.589</v>
+        <v>86.31399999999999</v>
       </c>
       <c r="K2" t="n">
         <v>186</v>
@@ -859,19 +865,19 @@
         <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>7.684</v>
+        <v>7.016</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.01</v>
+        <v>-1.21</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.762</v>
+        <v>-0.459</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.358</v>
+        <v>-2.785</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.834</v>
+        <v>2.566</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -892,40 +898,43 @@
         <v>2.8242</v>
       </c>
       <c r="AC2" t="n">
+        <v>2.8308</v>
+      </c>
+      <c r="AD2" t="n">
         <v>24.6</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>1.494</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>33</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>47.5</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>16.7</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>56.2</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>68.2</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>529</v>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>KO1+KO2+KO3</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>one clone holds 81% of the reads with a junction; read-weighted numbers are dominated by it, so compare clone_weighted_frequency_x1e3</t>
         </is>
@@ -952,19 +961,19 @@
         <v>344</v>
       </c>
       <c r="F3" t="n">
-        <v>133.2</v>
+        <v>133.205</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3872</v>
+        <v>0.387223</v>
       </c>
       <c r="H3" t="n">
-        <v>133.2</v>
+        <v>133.205</v>
       </c>
       <c r="I3" t="n">
-        <v>133.2</v>
+        <v>133.205</v>
       </c>
       <c r="J3" t="n">
-        <v>133.2</v>
+        <v>133.205</v>
       </c>
       <c r="K3" t="n">
         <v>336</v>
@@ -973,19 +982,19 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7.519</v>
+        <v>4.904</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.029999999999999</v>
+        <v>-5.89</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.497</v>
+        <v>-2.281</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.925</v>
+        <v>-3.636</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.068</v>
+        <v>-1.08</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1006,40 +1015,43 @@
         <v>22.465</v>
       </c>
       <c r="AC3" t="n">
+        <v>23.0088</v>
+      </c>
+      <c r="AD3" t="n">
         <v>91.8</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>11.884</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>33.4</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>49.4</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>15.7</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>48.7</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>70.7</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>529</v>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>KO1+KO2+KO3</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1062,19 +1074,19 @@
         <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>27.827</v>
+        <v>27.826</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3812</v>
+        <v>0.381177</v>
       </c>
       <c r="H4" t="n">
-        <v>27.827</v>
+        <v>27.826</v>
       </c>
       <c r="I4" t="n">
-        <v>27.827</v>
+        <v>27.826</v>
       </c>
       <c r="J4" t="n">
-        <v>27.827</v>
+        <v>28.2</v>
       </c>
       <c r="K4" t="n">
         <v>73</v>
@@ -1092,10 +1104,10 @@
         <v>-2.131</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.254</v>
+        <v>-4.166</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.011</v>
+        <v>0.374</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1116,40 +1128,43 @@
         <v>4.9338</v>
       </c>
       <c r="AC4" t="n">
+        <v>4.9744</v>
+      </c>
+      <c r="AD4" t="n">
         <v>36.6</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>2.61</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>37</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>56.2</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>19.2</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>55.6</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>529</v>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>KO1+KO2+KO3</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1175,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3794</v>
+        <v>0.379331</v>
       </c>
       <c r="H5" t="n">
         <v>1.586</v>
@@ -1184,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.829</v>
+        <v>5.284</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1202,10 +1217,10 @@
         <v>1.586</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.658</v>
+        <v>-1.415</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.829</v>
+        <v>5.284</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1231,20 +1246,23 @@
       <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>529</v>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>KO2+KO3</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1270,7 +1288,7 @@
         <v>0.76</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3798</v>
+        <v>0.379856</v>
       </c>
       <c r="H6" t="n">
         <v>0.76</v>
@@ -1279,7 +1297,7 @@
         <v>0.76</v>
       </c>
       <c r="J6" t="n">
-        <v>2.48</v>
+        <v>2.838</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -1294,13 +1312,13 @@
         <v>-3</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.139</v>
+        <v>-1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.996</v>
+        <v>-3.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.721</v>
+        <v>2.078</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1321,37 +1339,40 @@
         <v>0.1096</v>
       </c>
       <c r="AC6" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="AD6" t="n">
         <v>3.8</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>0.058</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>100</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>529</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>KO1+KO3</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1377,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3802</v>
+        <v>0.380227</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1386,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.49</v>
+        <v>2.875</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1404,10 +1425,10 @@
         <v>-0.445</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.384</v>
+        <v>-3.259</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.49</v>
+        <v>2.875</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1433,20 +1454,23 @@
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>529</v>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>KO1+KO2</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1459,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1471,9 +1495,9 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
@@ -1490,8 +1514,8 @@
     <col width="28" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
     <col width="28" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
     <col width="28" customWidth="1" min="33" max="33"/>
@@ -1500,22 +1524,32 @@
     <col width="28" customWidth="1" min="36" max="36"/>
     <col width="28" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="24" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
     <col width="28" customWidth="1" min="41" max="41"/>
     <col width="28" customWidth="1" min="42" max="42"/>
-    <col width="26" customWidth="1" min="43" max="43"/>
-    <col width="22" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="28" customWidth="1" min="43" max="43"/>
+    <col width="28" customWidth="1" min="44" max="44"/>
+    <col width="28" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
     <col width="28" customWidth="1" min="48" max="48"/>
-    <col width="24" customWidth="1" min="49" max="49"/>
-    <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="50" max="50"/>
     <col width="28" customWidth="1" min="51" max="51"/>
     <col width="28" customWidth="1" min="52" max="52"/>
-    <col width="28" customWidth="1" min="53" max="53"/>
-    <col width="15" customWidth="1" min="54" max="54"/>
+    <col width="26" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="28" customWidth="1" min="56" max="56"/>
+    <col width="28" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="24" customWidth="1" min="59" max="59"/>
+    <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="28" customWidth="1" min="62" max="62"/>
+    <col width="28" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1556,235 +1590,285 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>unique_density_x1e5_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unique_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>unique_density_x1e5_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_sd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>combined_density_x1e5_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>combined_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_sd</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>single_read_density_x1e5_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>single_read_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_sd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>clone_weighted_frequency_x1e3_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>clone_weighted_frequency_x1e3_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_mean</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_sd</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>mutation_frequency_x1e3_sensitivity_p_welch_log_half_event_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>mutation_frequency_x1e3_sensitivity_p_welch_log_third_of_smallest_vs_Aicda-_-</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_sd</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_mean</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_sd</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>pct_GC_mean</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>pct_GC_sd</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>pct_GC_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>pct_GC_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>pct_GC_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>pct_transitions_mean</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>pct_transitions_sd</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>pct_transitions_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>pct_transitions_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>pct_transitions_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_mean</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_sd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_welch_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_welch_log_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_mwu_vs_Aicda-_-</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>compared_with</t>
         </is>
@@ -1803,138 +1887,168 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>81.59399999999999</v>
+        <v>81.593</v>
       </c>
       <c r="E2" t="n">
-        <v>52.7197</v>
+        <v>52.7225</v>
       </c>
       <c r="F2" t="n">
-        <v>0.116124598171487</v>
+        <v>0.1161372984053289</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002669438986832193</v>
+        <v>0.002669426775960031</v>
       </c>
       <c r="H2" t="n">
+        <v>0.001170603581943498</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.001151609188852237</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.07652250047505924</v>
       </c>
-      <c r="I2" t="n">
-        <v>81.59399999999999</v>
-      </c>
-      <c r="J2" t="n">
-        <v>52.7197</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.1173682473390214</v>
+        <v>81.593</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002072392326471892</v>
+        <v>52.7225</v>
       </c>
       <c r="M2" t="n">
+        <v>0.1173810776049017</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002072589292199202</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004782797788365905</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.003042812293251674</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.1</v>
       </c>
-      <c r="N2" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.3675</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.1341976722207809</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.4278836585820493</v>
-      </c>
       <c r="R2" t="n">
+        <v>-1.6237</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.0114</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1888075819247015</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4277597901585383</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4260824195687803</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.4226497308103742</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.2</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
         <v>15.5131</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>9.8248</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>0.1126628000954235</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AB2" t="n">
+        <v>0.001744735985441827</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.002618937026243271</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.001595338507869068</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AE2" t="n">
         <v>0.07652250047505924</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AF2" t="n">
         <v>10.0743</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AG2" t="n">
         <v>10.7823</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AH2" t="n">
         <v>0.2481884881575702</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AI2" t="n">
+        <v>0.01430223370012521</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.02247891737334207</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.005152107225631051</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.07652250047505924</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>51</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>35.8396</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.1376101259806452</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.004107693748381547</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.07652250047505924</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5.3293</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5.7039</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.2481885102701591</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.005153313131487974</v>
       </c>
       <c r="AL2" t="n">
         <v>0.07652250047505924</v>
       </c>
       <c r="AM2" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>35.8396</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.1376101259806452</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.03267649585034776</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.07652250047505924</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.3293</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.7039</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.2481885102701591</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.0143087023066126</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.07652250047505924</v>
+      </c>
+      <c r="AW2" t="n">
         <v>34.4667</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AX2" t="n">
         <v>2.203</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>51.0333</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.5742</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.1677</v>
       </c>
       <c r="BA2" t="n">
         <v>0.5</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>51.0333</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.5742</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.1677</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>Aicda-/-</t>
         </is>
@@ -1958,52 +2072,52 @@
       <c r="E3" t="n">
         <v>0.4388</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.782</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.7932</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.4161</v>
+      <c r="R3" t="n">
+        <v>0.0003</v>
       </c>
       <c r="S3" t="n">
+        <v>1.4165</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0788</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>0.1364</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AF3" t="n">
         <v>0.0365</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
         <v>0.0633</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AM3" t="n">
         <v>1.2667</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AN3" t="n">
         <v>2.1939</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AR3" t="n">
         <v>0.0193</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AS3" t="n">
         <v>0.0335</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AW3" t="n">
         <v>100</v>
       </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
